--- a/AAII_Financials/Yearly/NCEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NCEL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>NCEL</t>
   </si>
@@ -877,8 +877,8 @@
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>300</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -908,10 +908,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
@@ -949,10 +949,10 @@
         <v>2600</v>
       </c>
       <c r="E17" s="3">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="F17" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="G17" s="3">
         <v>6300</v>
@@ -979,10 +979,10 @@
         <v>-2600</v>
       </c>
       <c r="E18" s="3">
-        <v>-1800</v>
+        <v>-2100</v>
       </c>
       <c r="F18" s="3">
-        <v>-3100</v>
+        <v>-3000</v>
       </c>
       <c r="G18" s="3">
         <v>-6300</v>
@@ -1020,13 +1020,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>5200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>200</v>
@@ -1050,13 +1050,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2200</v>
+        <v>-2600</v>
       </c>
       <c r="E21" s="3">
-        <v>-6900</v>
+        <v>-1700</v>
       </c>
       <c r="F21" s="3">
-        <v>-3200</v>
+        <v>-2500</v>
       </c>
       <c r="G21" s="3">
         <v>-5900</v>
@@ -1083,10 +1083,10 @@
         <v>6000</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1113,10 +1113,10 @@
         <v>-8300</v>
       </c>
       <c r="E23" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="F23" s="3">
-        <v>-3400</v>
+        <v>-3300</v>
       </c>
       <c r="G23" s="3">
         <v>-6500</v>
@@ -1142,11 +1142,11 @@
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-100</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>-8300</v>
       </c>
       <c r="E26" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="F26" s="3">
         <v>-3300</v>
@@ -1233,7 +1233,7 @@
         <v>-8300</v>
       </c>
       <c r="E27" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="F27" s="3">
         <v>-3300</v>
@@ -1380,13 +1380,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-5200</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>-200</v>
@@ -1413,7 +1413,7 @@
         <v>-8300</v>
       </c>
       <c r="E33" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="F33" s="3">
         <v>-3300</v>
@@ -1473,7 +1473,7 @@
         <v>-8300</v>
       </c>
       <c r="E35" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="F35" s="3">
         <v>-3300</v>
@@ -1622,8 +1622,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -1682,8 +1682,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>500</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2011,7 +2011,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
@@ -2044,7 +2044,7 @@
         <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>2700</v>
+        <v>7700</v>
       </c>
       <c r="F58" s="3">
         <v>1800</v>
@@ -2074,7 +2074,7 @@
         <v>1700</v>
       </c>
       <c r="E59" s="3">
-        <v>5500</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
         <v>1000</v>
@@ -2448,7 +2448,7 @@
         <v>-84900</v>
       </c>
       <c r="E72" s="3">
-        <v>-75300</v>
+        <v>-76600</v>
       </c>
       <c r="F72" s="3">
         <v>-68800</v>
@@ -2663,7 +2663,7 @@
         <v>-8300</v>
       </c>
       <c r="E81" s="3">
-        <v>-7300</v>
+        <v>-7200</v>
       </c>
       <c r="F81" s="3">
         <v>-3300</v>
@@ -2887,10 +2887,10 @@
         <v>-2800</v>
       </c>
       <c r="E89" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="F89" s="3">
-        <v>-3100</v>
+        <v>-3400</v>
       </c>
       <c r="G89" s="3">
         <v>-5700</v>
@@ -3021,7 +3021,7 @@
         <v>1700</v>
       </c>
       <c r="E94" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>100</v>
@@ -3185,10 +3185,10 @@
         <v>2600</v>
       </c>
       <c r="E100" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F100" s="3">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="G100" s="3">
         <v>1100</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -3245,10 +3245,10 @@
         <v>1600</v>
       </c>
       <c r="E102" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="F102" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="G102" s="3">
         <v>-4800</v>
